--- a/data/nzd0584/nzd0584.xlsx
+++ b/data/nzd0584/nzd0584.xlsx
@@ -29799,9 +29799,15 @@
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="F2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.0484</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.0512</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -29849,9 +29855,15 @@
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.0454</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.0509</v>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
@@ -29899,9 +29911,15 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.0538</v>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
@@ -29949,9 +29967,15 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="F5" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.0493</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.061</v>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
@@ -29999,9 +30023,15 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="F6" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.046</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.0555</v>
+      </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
@@ -30049,9 +30079,15 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="F7" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0441</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.0514</v>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
@@ -30099,9 +30135,15 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.0437</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.047</v>
+      </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
@@ -30149,9 +30191,15 @@
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="F9" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0543</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0618</v>
+      </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
@@ -30199,9 +30247,15 @@
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="F10" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0561</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.06710000000000001</v>
+      </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
@@ -30249,9 +30303,15 @@
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="F11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.0147</v>
+      </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
@@ -30299,9 +30359,15 @@
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.1667</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
@@ -30349,9 +30415,15 @@
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="F13" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
@@ -30399,9 +30471,15 @@
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="F14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1759</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
@@ -30449,9 +30527,15 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="F15" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.1702</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
@@ -30499,9 +30583,15 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="F16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.1602</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -30549,9 +30639,15 @@
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="F17" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.1656</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
@@ -30599,9 +30695,15 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="F18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.1622</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
@@ -30649,9 +30751,15 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="F19" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.1627</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
@@ -30699,9 +30807,15 @@
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="F20" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1576</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
@@ -30749,9 +30863,15 @@
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="F21" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0459</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
@@ -30799,9 +30919,15 @@
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="F22" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.0357</v>
+      </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
@@ -30849,9 +30975,15 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="F23" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0237</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.0334</v>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
@@ -30899,9 +31031,15 @@
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="F24" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1534</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.2</v>
+      </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
@@ -30949,9 +31087,15 @@
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="F25" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.029</v>
+      </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
@@ -30999,9 +31143,15 @@
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="F26" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0146</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.0162</v>
+      </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
@@ -31049,9 +31199,15 @@
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="F27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0268</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.0355</v>
+      </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
@@ -31099,9 +31255,15 @@
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="F28" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0269</v>
+      </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
@@ -31149,9 +31311,15 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="F29" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0148</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.0184</v>
+      </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
@@ -31199,9 +31367,15 @@
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="F30" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.0149</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.022</v>
+      </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
@@ -31249,9 +31423,15 @@
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="F31" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.0188</v>
+      </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
@@ -31299,9 +31479,15 @@
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="F32" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.014</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.0164</v>
+      </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
@@ -31349,9 +31535,15 @@
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="F33" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.0179</v>
+      </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
@@ -31399,9 +31591,15 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="F34" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.0131</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.017</v>
+      </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
@@ -31449,9 +31647,15 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="F35" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.0118</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.0173</v>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
@@ -31499,9 +31703,15 @@
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="F36" t="n">
+        <v>0.015</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.0135</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.021</v>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
@@ -31549,9 +31759,15 @@
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="F37" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.0192</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.0454</v>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
